--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128149564</v>
       </c>
       <c r="B3" t="n">
-        <v>96815</v>
+        <v>96816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128149564</v>
       </c>
       <c r="B3" t="n">
-        <v>96816</v>
+        <v>96817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153517</v>
       </c>
       <c r="B2" t="n">
-        <v>58002</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128149564</v>
       </c>
       <c r="B3" t="n">
-        <v>96817</v>
+        <v>96825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153517</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128149564</v>
       </c>
       <c r="B3" t="n">
-        <v>96825</v>
+        <v>96918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>128153516</v>
       </c>
       <c r="B4" t="n">
-        <v>57267</v>
+        <v>57279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Böckert, Bettina Ekdahl</t>
+          <t>Bettina Ekdahl, Malin Böckert</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128153517</v>
       </c>
       <c r="B2" t="n">
-        <v>58015</v>
+        <v>58019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>128149564</v>
       </c>
       <c r="B3" t="n">
-        <v>96918</v>
+        <v>96930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bettina Ekdahl, Malin Böckert</t>
+          <t>Malin Böckert, Bettina Ekdahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -877,7 +877,7 @@
         <v>128153516</v>
       </c>
       <c r="B4" t="n">
-        <v>57279</v>
+        <v>57283</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128149564</v>
       </c>
       <c r="B3" t="n">
-        <v>96930</v>
+        <v>96932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Böckert, Bettina Ekdahl</t>
+          <t>Bettina Ekdahl, Malin Böckert</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -867,7 +867,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bettina Ekdahl, Malin Böckert</t>
+          <t>Malin Böckert, Bettina Ekdahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 38101-2024 artfynd.xlsx
+++ b/artfynd/A 38101-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128149564</v>
       </c>
       <c r="B3" t="n">
-        <v>96932</v>
+        <v>96933</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
